--- a/光伏配储项目/电价数据/2026/粤海厂.xlsx
+++ b/光伏配储项目/电价数据/2026/粤海厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5579700000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.56825</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.69486</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.27684</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.02743</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.84372</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46012</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.48103</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.56432</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.05254</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.8009500000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.57496</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.8929199999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.91916</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.43303</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.47887</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.27105</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.38083</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.81372</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.8627899999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.55314</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.8425900000000001</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.55177</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.57492</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.9240700000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.47604</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.9253899999999999</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.8730599999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>1.18431</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>1.09932</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.24274</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.56831</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.68283</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.8314400000000001</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.50163</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.35228</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.15926</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.41019</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.63664</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.25573</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.48962</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.63468</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.54047</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.39557</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.61696</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.52988</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.47016</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.89964</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47992</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4221</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.32831</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.10348</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.21978</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53761</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5227200000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53688</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49888</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42183</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.58023</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.86876</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.73189</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.47999</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43257</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.4367200000000001</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.11227</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.30958</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.9345399999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.20119</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.21976</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.8336699999999999</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.63932</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.43998</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.45056</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.73313</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.40854</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.17496</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1.00182</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.43128</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.3583</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.36519</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.72437</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.6007</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.48799</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.39236</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.38543</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.37841</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.19391</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.16516</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.16561</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19159</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.71795</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.38836</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.22949</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.57533</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.40719</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.49473</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.2879</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.8286699999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7572300000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91335</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.57962</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.46881</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.48591</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8915700000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.94485</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.8986499999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.66822</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6419</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.44542</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.8601599999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.30474</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.79098</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.8449099999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.35438</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.23811</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.38933</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.89958</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>1.16872</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.40904</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.40066</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.99781</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5845399999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.71075</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.32507</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.19328</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.39708</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.70104</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.52604</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.38351</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.2617</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.24334</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.71236</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.42883</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.43695</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.79105</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.46817</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.43983</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.2497</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.24342</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.26453</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.25052</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.43514</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.34785</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.4756</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.85858</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.82048</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.58628</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.28107</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.71897</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.56532</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.45194</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.42613</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48223</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.7484400000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.76136</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.99317</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.35475</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.36618</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>1.00216</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.74848</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.70294</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.95782</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.06072</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.31581</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.46983</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.17893</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.48875</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.82438</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.09868</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.57478</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.5340199999999999</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.7571100000000001</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.26465</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.35977</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.36917</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.31955</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.2049</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.08837</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>1.05234</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.54515</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.67965</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.93364</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.57059</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.47438</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.96923</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.28919</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.33134</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.20563</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.38775</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.4619</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.50551</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.38666</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.47041</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.29575</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.22589</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18762</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.37331</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.44808</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.43472</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.40734</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.26578</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.84666</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.57948</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.86675</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32379</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.78584</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.52942</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40749</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.51954</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.54799</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.5684900000000001</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.51415</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.93592</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.67818</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.77432</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.80135</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.93592</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.77996</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.6073</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.6073</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.59712</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.65551</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.52419</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.19526</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5870599999999999</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.54118</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.58217</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.48478</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.7431</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5696599999999999</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.5415399999999999</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.5486599999999999</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.54395</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.69516</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.42973</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.56035</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.5512400000000001</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.5229400000000001</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34652</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.37173</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.16852</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.17959</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.6147899999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.43321</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.08367000000000001</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08513</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.13818</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.46078</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.46965</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.46298</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.5419400000000001</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.46854</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33548</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.44439</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.4104100000000001</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.89246</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.05303</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.80471</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.80526</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.87754</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>1.13071</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.58375</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.51501</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.85045</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.8492000000000001</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>1.06342</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.70351</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.61515</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14266</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.82586</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.87399</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.7392799999999999</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.67522</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.8041699999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.8041699999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.83775</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.66901</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.8252200000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.10243</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.57256</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.61363</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.63099</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.94775</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.55457</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.17864</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.57344</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.58821</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.8628400000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80787</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88273</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.509</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41996</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4679</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22706</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54315</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42081</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43802</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5708300000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6695800000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.06851</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.70612</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56538</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.6197699999999999</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.58597</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.01107</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.35855</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.33269</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27198</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5814900000000001</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.79171</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5974299999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.68767</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.60219</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>1.20016</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.8515900000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7939400000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6959500000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.6290399999999999</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.19712</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.97562</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.71837</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.7221900000000001</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.51288</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.70224</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.67476</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.72368</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.7497200000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.6772899999999999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.7241599999999999</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.7599900000000001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.67331</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.72545</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.71638</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.59853</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.70236</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.7465499999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.9157999999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.7241599999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.8873799999999999</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.74161</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.72376</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.71997</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.69865</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.67638</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.6661</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.67757</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.54365</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.5189900000000001</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95126</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47643</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47953</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.53887</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.64498</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.69877</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.87674</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.0622</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.38716</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.99411</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.6480900000000001</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.19544</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>1.00529</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>1.12827</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.03272</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.7353099999999999</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.98219</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.26488</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.42196</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>1.06244</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.72959</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.04469</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.91034</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.48976</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.94262</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.98246</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.72114</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.87749</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.43241</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.49435</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.41481</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.45411</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50668</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43243</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42605</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.42109</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.2253</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.54595</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7027100000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79416</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64895</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5828300000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.44808</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.87913</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.31918</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.00017</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.7395700000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.69568</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.69215</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.45005</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.73145</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.19029</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.74428</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9806699999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.7284299999999999</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.31463</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.22741</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.79453</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.66709</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.45053</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6767799999999999</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.9426599999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.65918</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.8384400000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.19354</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.21633</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9632999999999999</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1.07052</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1.02402</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.25618</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.35697</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.35006</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.76145</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>1.14749</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.1844</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.35341</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>1.13138</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.17592</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.71002</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>1.08836</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.15138</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.20498</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>1.05869</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>1.03787</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>1.13301</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.20416</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.8431900000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3248</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43914</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.49019</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.43446</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.43497</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.48215</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.4715299999999999</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.4825</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6984199999999999</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45807</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.61899</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.50224</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.72421</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.61693</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62037</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.83911</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.24768</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.1476</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.83928</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.44818</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.69294</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.93779</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.1667</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.11697</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.1135</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5461</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43759</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49671</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.45397</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.43149</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5810299999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.47868</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.42179</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.0696</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.0579</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>1.04628</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.0472</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.53502</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.58517</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9290499999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08549</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.00495</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.70127</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.69127</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.77998</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.27004</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.74609</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.32562</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.21058</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.04119</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.69127</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.67627</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.70893</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.72127</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.71637</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.69319</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.71627</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20602</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.75141</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.74769</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.75602</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.76343</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.67899</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.79771</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.00388</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.11097</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.74239</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.75003</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.74444</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.77354</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.86126</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.7006699999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.47637</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.09439</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.48039</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34823</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.50262</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.13869</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49729</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.5299400000000001</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.53998</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28501</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.46061</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.97233</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.53118</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.24471</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.88855</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.75709</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.46536</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.49864</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.51471</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45933</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34925</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.46123</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.53479</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.5147200000000001</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.41469</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.43699</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5654600000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.43227</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.46263</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.68855</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45604</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64109</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.81675</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46773</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44705</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51207</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41677</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54318</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7509400000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7553799999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.5297000000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.49666</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.71735</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.74859</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5452400000000001</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.49599</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.44634</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.00273</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.45304</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.4319</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.08314</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.1164</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.06987</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.10365</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12186</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01165</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.13493</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.12133</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.33904</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.88648</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.56585</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.74224</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9498799999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.6688200000000001</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.37009</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.70609</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7834099999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.64733</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.31082</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56031</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.59272</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.47102</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.58192</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.87646</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.41125</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.46677</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.79546</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.48634</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.06127</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.71877</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.54349</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.53634</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.60478</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.6593300000000001</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.85405</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.33782</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.79025</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1.08732</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.77212</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>1.10975</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>1.03671</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.24151</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.24501</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.59234</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.42412</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.50149</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.35906</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.31754</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.65018</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.09265</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47597</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.19097</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6566900000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.45426</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.51475</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.56926</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.78862</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.7725599999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.75187</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.47666</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.18499</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.67615</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.84388</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.26753</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.34818</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.50406</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.22999</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5471</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5586599999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5596599999999999</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.41777</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.5242899999999999</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23516</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.50171</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.47071</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.53455</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.44878</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.44896</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.6565800000000001</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.78754</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.20575</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.59901</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43172</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.42262</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.43684</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.47587</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.54438</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.50701</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.46415</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.65107</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40589</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.47385</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.47121</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.6025199999999999</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41365</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.47108</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.47873</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.352</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.7931</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.24088</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.9559</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.45515</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.7646499999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.62917</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.54691</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.42108</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40362</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.44026</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.48166</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.5271699999999999</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.16044</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.49905</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.69782</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.67571</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5508500000000001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.80604</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.81255</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.53599</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.43021</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.44507</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.42584</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.43503</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.46815</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.5893999999999999</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.44346</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.46168</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.44168</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.4734</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.47021</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.80404</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.43059</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.23855</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.24287</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.39935</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.24422</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.17481</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.50588</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.78262</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.59265</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.53589</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.63163</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.8255399999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5985199999999999</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.82933</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.8228</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.64112</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.53698</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.6859500000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.82278</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.38976</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.65608</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.89012</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.72827</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.45067</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1.21221</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.04209</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1.12212</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.7859400000000001</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>1.15331</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.38451</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.10877</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.20012</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.19034</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.7461</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.50387</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.11995</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41777</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.79731</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34725</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.57666</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.56823</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7939700000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7964600000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.58148</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.48238</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.47086</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.42668</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.7007899999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.6286499999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6061</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.57598</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.53247</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.83031</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.31374</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.22316</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.13411</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.23568</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.1426</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.16643</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.77418</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5563400000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.6269</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.49632</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.54511</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.69104</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.6405</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.10473</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.71415</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.57047</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.51783</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.51612</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.49675</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.51528</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.49572</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.5139400000000001</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5757899999999999</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.58105</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.51439</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.43105</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.51607</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.58199</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.68996</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.31036</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.21564</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.68653</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.6057400000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.26043</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.91747</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6881699999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.29724</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.98476</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.52787</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.52689</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.51416</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.55118</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34594</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.5130399999999999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.49644</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.42948</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6551</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.62763</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.71726</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.1941</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.50936</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1.13428</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.17382</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.12892</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>1.10236</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1.13691</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.11391</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>1.10601</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>1.11679</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.78273</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.63567</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.09852</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.7059299999999999</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.08961</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.08002</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.06148</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.89843</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1.10284</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1.01868</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>1.0862</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.59491</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.30527</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.11391</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.51593</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.41829</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.10882</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.18615</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.01545</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.83773</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.8354600000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.79311</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69887</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.6179600000000001</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.71797</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.83626</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.78707</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.42428</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.83929</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.79796</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.49314</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.55052</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.5412400000000001</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.46863</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.1974</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>1.09897</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.18969</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.14039</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.2077</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.1867</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.1847</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.23641</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.25484</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.1577</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.76998</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.78949</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.81985</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.0079</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.22832</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.21077</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.50296</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.50462</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.31993</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.26325</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.43439</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.03785</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.46949</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.42824</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.73621</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.5008</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.50143</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.79588</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.44215</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.51151</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.7982899999999999</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.28935</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.98725</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.91225</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.93925</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.04905</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.17342</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.11815</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.85772</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6838500000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.32202</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.24061</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.24666</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.12715</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.68641</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.06591</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.77574</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.08013</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.08063</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.12079</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.0792</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5099900000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.75582</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.6188400000000001</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15151</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.84178</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.7609600000000001</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.15443</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.93388</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.03342</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.25355</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.04818</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.09613</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.0323</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.04419</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.16572</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.1539</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.17183</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.18567</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.47569</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.15667</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.27129</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.10308</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.08449</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.10937</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.15906</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.15826</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.30968</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.7787000000000001</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6958300000000001</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37614</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.63483</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.29084</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.29241</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.05099</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.49384</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5169900000000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.6341</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.79332</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.8084</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.75759</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.02848</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.04159</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.27274</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.44639</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.61856</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.60107</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.44796</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.70641</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.36372</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.63721</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7529400000000001</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70324</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50411</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.02173</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.41912</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.81438</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.59537</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.6291599999999999</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.74905</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.7585</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.70871</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.28869</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.2628</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.45132</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.26677</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.23722</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.24971</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.24115</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.21211</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.17612</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.22751</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.31607</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.19917</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.21099</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.18916</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.25903</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.60917</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.82631</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80115</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56336</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.31594</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55763</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55322</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5648500000000001</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51452</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55241</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41936</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5199400000000001</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45887</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45886</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43813</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41182</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49355</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49882</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54539</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.51807</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5188700000000001</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5540499999999999</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17017</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8793099999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.48593</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.36731</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50152</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.57289</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79703</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59782</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.52313</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.51178</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5549299999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.16586</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.69639</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.22708</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5420199999999999</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.57828</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79595</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.54901</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7868099999999999</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.16872</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79553</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68076</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.2663</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.19953</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.21514</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.21331</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.81021</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.75018</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.70377</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.72711</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.7376699999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.74234</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.81971</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.64228</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8556900000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.59792</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.71399</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.67811</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.62098</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61124</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7919299999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.70098</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.89095</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.68923</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.59892</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.52019</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37242</v>
       </c>
     </row>
   </sheetData>
